--- a/artfynd/A 8071-2022 artfynd.xlsx
+++ b/artfynd/A 8071-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961482</v>
+        <v>119961480</v>
       </c>
       <c r="B2" t="n">
         <v>56233</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/artfynd/A 8071-2022 artfynd.xlsx
+++ b/artfynd/A 8071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119961480</v>
       </c>
       <c r="B2" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 8071-2022 artfynd.xlsx
+++ b/artfynd/A 8071-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961480</v>
+        <v>119961482</v>
       </c>
       <c r="B2" t="n">
         <v>56243</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/artfynd/A 8071-2022 artfynd.xlsx
+++ b/artfynd/A 8071-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119961482</v>
+        <v>119961480</v>
       </c>
       <c r="B2" t="n">
         <v>56243</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
